--- a/experiment_difficulty.xlsx
+++ b/experiment_difficulty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hackerman/misty_py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263C2B2A-BA79-4243-89E0-B50C03915FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E50933A-B040-F842-81BA-60606ADD5669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{D2F472C4-A835-AE43-9DD9-971719870CAB}"/>
   </bookViews>
@@ -50,12 +50,6 @@
     <t>easy2</t>
   </si>
   <si>
-    <t>medium1</t>
-  </si>
-  <si>
-    <t>medium2</t>
-  </si>
-  <si>
     <t>hard</t>
   </si>
   <si>
@@ -75,6 +69,12 @@
   </si>
   <si>
     <t>07</t>
+  </si>
+  <si>
+    <t>med1</t>
+  </si>
+  <si>
+    <t>med2</t>
   </si>
 </sst>
 </file>
@@ -458,7 +458,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -469,7 +469,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -480,40 +480,40 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/experiment_difficulty.xlsx
+++ b/experiment_difficulty.xlsx
@@ -1,74 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stummuac-my.sharepoint.com/personal/46057371_ad_mmu_ac_uk/Documents/Experiments/_labusers/OliC/misty_py-studyBranch/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_3F5640DBF424BCE2C6FD4F6705F318F5FCD1A737" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F0D2F3E-8DE0-4103-8B4B-4C557A417E57}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="5820" yWindow="2625" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t xml:space="preserve">exp_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diffbyt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">easy1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">easy2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">med1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">med2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>exp_diff</t>
+  </si>
+  <si>
+    <t>exp_time</t>
+  </si>
+  <si>
+    <t>diffbyt</t>
+  </si>
+  <si>
+    <t>easy1</t>
+  </si>
+  <si>
+    <t>easy2</t>
+  </si>
+  <si>
+    <t>med1</t>
+  </si>
+  <si>
+    <t>med2</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>E0</t>
+  </si>
+  <si>
+    <t>C0</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -77,19 +71,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -101,7 +87,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -109,101 +95,82 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{0D8A3E1A-E991-4E6E-BDD3-037C41CC268A}"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -235,7 +202,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -259,7 +226,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -319,95 +286,89 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="10.55078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2">
         <v>120</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="B3">
+        <v>120</v>
+      </c>
+      <c r="C3" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>120</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>120</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>120</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>120</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>120</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>120</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>